--- a/full/sliding_window_results_window_5.xlsx
+++ b/full/sliding_window_results_window_5.xlsx
@@ -463,13 +463,13 @@
         <v>29.54</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>29.49466895192899</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.54</v>
+        <v>-0.04533104807100585</v>
       </c>
       <c r="E2" t="n">
-        <v>872.6116</v>
+        <v>0.002054903919215843</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.55</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>30.36079783735651</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.55</v>
+        <v>0.8107978373565139</v>
       </c>
       <c r="E3" t="n">
-        <v>873.2025</v>
+        <v>0.657393133062</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.75</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>30.1949703584952</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.75</v>
+        <v>0.4449703584951976</v>
       </c>
       <c r="E4" t="n">
-        <v>885.0625</v>
+        <v>0.1979986199393447</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.84</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>29.99044595807602</v>
       </c>
       <c r="D5" t="n">
-        <v>-29.84</v>
+        <v>0.1504459580760162</v>
       </c>
       <c r="E5" t="n">
-        <v>890.4256</v>
+        <v>0.02263398630141044</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.81</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>29.95599739102165</v>
       </c>
       <c r="D6" t="n">
-        <v>-29.81</v>
+        <v>0.1459973910216554</v>
       </c>
       <c r="E6" t="n">
-        <v>888.6360999999999</v>
+        <v>0.02131523818513015</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>29.86940292917211</v>
       </c>
       <c r="D7" t="n">
-        <v>-29.92</v>
+        <v>-0.05059707082789089</v>
       </c>
       <c r="E7" t="n">
-        <v>895.2064000000001</v>
+        <v>0.002560063576362607</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.98</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30.08088788470883</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.98</v>
+        <v>0.100887884708829</v>
       </c>
       <c r="E8" t="n">
-        <v>898.8004000000001</v>
+        <v>0.01017836528102198</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.04</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>30.14308335558982</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.04</v>
+        <v>0.1030833555898241</v>
       </c>
       <c r="E9" t="n">
-        <v>902.4015999999999</v>
+        <v>0.01062617819965811</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.21</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>30.15444665640283</v>
       </c>
       <c r="D10" t="n">
-        <v>-30.21</v>
+        <v>-0.05555334359717534</v>
       </c>
       <c r="E10" t="n">
-        <v>912.6441000000001</v>
+        <v>0.003086173984825823</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.22</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>30.41531845668382</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.22</v>
+        <v>0.1953184566838218</v>
       </c>
       <c r="E11" t="n">
-        <v>913.2483999999999</v>
+        <v>0.03814929952134995</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.38</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30.1655915532424</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.38</v>
+        <v>-0.2144084467575986</v>
       </c>
       <c r="E12" t="n">
-        <v>922.9444</v>
+        <v>0.045970982041006</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.44</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>30.31270043564337</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.44</v>
+        <v>-0.1272995643566297</v>
       </c>
       <c r="E13" t="n">
-        <v>926.5936</v>
+        <v>0.01620517908538771</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.48</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>30.46299789611383</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.48</v>
+        <v>-0.01700210388616696</v>
       </c>
       <c r="E14" t="n">
-        <v>929.0304</v>
+        <v>0.0002890715365560138</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.69</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>30.37324704666575</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.69</v>
+        <v>-0.3167529533342552</v>
       </c>
       <c r="E15" t="n">
-        <v>941.8761000000001</v>
+        <v>0.1003324334459729</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.75</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>30.12706205312848</v>
       </c>
       <c r="D16" t="n">
-        <v>-30.75</v>
+        <v>-0.6229379468715237</v>
       </c>
       <c r="E16" t="n">
-        <v>945.5625</v>
+        <v>0.3880516856525093</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.94</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>30.34781970634466</v>
       </c>
       <c r="D17" t="n">
-        <v>-30.94</v>
+        <v>-0.5921802936553426</v>
       </c>
       <c r="E17" t="n">
-        <v>957.2836000000001</v>
+        <v>0.3506775001937278</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.95</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>30.50366043477329</v>
       </c>
       <c r="D18" t="n">
-        <v>-30.95</v>
+        <v>-0.4463395652267117</v>
       </c>
       <c r="E18" t="n">
-        <v>957.9024999999999</v>
+        <v>0.19921900748677</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.02</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>30.65607259769465</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.02</v>
+        <v>-0.3639274023053538</v>
       </c>
       <c r="E19" t="n">
-        <v>962.2404</v>
+        <v>0.1324431541487228</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.12</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>30.81190346429251</v>
       </c>
       <c r="D20" t="n">
-        <v>-31.12</v>
+        <v>-0.3080965357074881</v>
       </c>
       <c r="E20" t="n">
-        <v>968.4544000000001</v>
+        <v>0.09492347531495547</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.28</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>31.18871156966965</v>
       </c>
       <c r="D21" t="n">
-        <v>-31.28</v>
+        <v>-0.09128843033035139</v>
       </c>
       <c r="E21" t="n">
-        <v>978.4384000000001</v>
+        <v>0.008333577512179419</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.38</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>31.34030125405312</v>
       </c>
       <c r="D22" t="n">
-        <v>-31.38</v>
+        <v>-0.03969874594687539</v>
       </c>
       <c r="E22" t="n">
-        <v>984.7044</v>
+        <v>0.001575990429754555</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.58</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>31.54362987658435</v>
       </c>
       <c r="D23" t="n">
-        <v>-31.58</v>
+        <v>-0.03637012341564372</v>
       </c>
       <c r="E23" t="n">
-        <v>997.2963999999999</v>
+        <v>0.001322785877269155</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.65</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>31.55541674467346</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.65</v>
+        <v>-0.09458325532654044</v>
       </c>
       <c r="E24" t="n">
-        <v>1001.7225</v>
+        <v>0.00894599218816554</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.88</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>31.83179620430884</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.88</v>
+        <v>-0.04820379569115474</v>
       </c>
       <c r="E25" t="n">
-        <v>1016.3344</v>
+        <v>0.002323605919034588</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.28</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>32.25044675589361</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.28</v>
+        <v>-0.02955324410639548</v>
       </c>
       <c r="E26" t="n">
-        <v>1041.9984</v>
+        <v>0.0008733942372121993</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.45</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>32.25729989508818</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.45</v>
+        <v>-0.1927001049118218</v>
       </c>
       <c r="E27" t="n">
-        <v>1053.0025</v>
+        <v>0.03713333043302711</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.85</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>33.36429149320447</v>
       </c>
       <c r="D28" t="n">
-        <v>-32.85</v>
+        <v>0.5142914932044675</v>
       </c>
       <c r="E28" t="n">
-        <v>1079.1225</v>
+        <v>0.2644957399824809</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.9</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>33.14803942832026</v>
       </c>
       <c r="D29" t="n">
-        <v>-32.9</v>
+        <v>0.2480394283202614</v>
       </c>
       <c r="E29" t="n">
-        <v>1082.41</v>
+        <v>0.06152355800144208</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>33.38757620345185</v>
       </c>
       <c r="D30" t="n">
-        <v>-33.1</v>
+        <v>0.2875762034518488</v>
       </c>
       <c r="E30" t="n">
-        <v>1095.61</v>
+        <v>0.08270007279177911</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.4</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>33.28909050317021</v>
       </c>
       <c r="D31" t="n">
-        <v>-33.4</v>
+        <v>-0.110909496829791</v>
       </c>
       <c r="E31" t="n">
-        <v>1115.56</v>
+        <v>0.01230091648703742</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.7</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>33.92475531782942</v>
       </c>
       <c r="D32" t="n">
-        <v>-33.7</v>
+        <v>0.2247553178294197</v>
       </c>
       <c r="E32" t="n">
-        <v>1135.69</v>
+        <v>0.05051495289260347</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.1</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>34.66902840265841</v>
       </c>
       <c r="D33" t="n">
-        <v>-34.1</v>
+        <v>0.5690284026584038</v>
       </c>
       <c r="E33" t="n">
-        <v>1162.81</v>
+        <v>0.3237933230319746</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.4</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>34.63718235691104</v>
       </c>
       <c r="D34" t="n">
-        <v>-34.4</v>
+        <v>0.2371823569110418</v>
       </c>
       <c r="E34" t="n">
-        <v>1183.36</v>
+        <v>0.05625547042987684</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.9</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>35.05672620621896</v>
       </c>
       <c r="D35" t="n">
-        <v>-34.9</v>
+        <v>0.1567262062189627</v>
       </c>
       <c r="E35" t="n">
-        <v>1218.01</v>
+        <v>0.02456310371578883</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>35.3</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>34.87466341241493</v>
       </c>
       <c r="D36" t="n">
-        <v>-35.3</v>
+        <v>-0.4253365875850719</v>
       </c>
       <c r="E36" t="n">
-        <v>1246.09</v>
+        <v>0.1809112127385135</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>35.7</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>35.17604680191488</v>
       </c>
       <c r="D37" t="n">
-        <v>-35.7</v>
+        <v>-0.523953198085124</v>
       </c>
       <c r="E37" t="n">
-        <v>1274.49</v>
+        <v>0.2745269537836292</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>36.3</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>35.79052169454162</v>
       </c>
       <c r="D38" t="n">
-        <v>-36.3</v>
+        <v>-0.50947830545838</v>
       </c>
       <c r="E38" t="n">
-        <v>1317.69</v>
+        <v>0.2595681437327424</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>36.8</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>36.17600804826044</v>
       </c>
       <c r="D39" t="n">
-        <v>-36.8</v>
+        <v>-0.623991951739562</v>
       </c>
       <c r="E39" t="n">
-        <v>1354.24</v>
+        <v>0.3893659558357479</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>37.3</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>37.20473327999652</v>
       </c>
       <c r="D40" t="n">
-        <v>-37.3</v>
+        <v>-0.09526672000347958</v>
       </c>
       <c r="E40" t="n">
-        <v>1391.29</v>
+        <v>0.009075747940221375</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>37.9</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>37.80274794948554</v>
       </c>
       <c r="D41" t="n">
-        <v>-37.9</v>
+        <v>-0.09725205051446295</v>
       </c>
       <c r="E41" t="n">
-        <v>1436.41</v>
+        <v>0.009457961329267654</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>38.5</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>38.56262667401201</v>
       </c>
       <c r="D42" t="n">
-        <v>-38.5</v>
+        <v>0.06262667401200872</v>
       </c>
       <c r="E42" t="n">
-        <v>1482.25</v>
+        <v>0.003922100297806408</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>38.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>39.44100861461524</v>
       </c>
       <c r="D43" t="n">
-        <v>-38.9</v>
+        <v>0.5410086146152366</v>
       </c>
       <c r="E43" t="n">
-        <v>1513.21</v>
+        <v>0.2926903210878977</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>39.4</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>40.17533049045248</v>
       </c>
       <c r="D44" t="n">
-        <v>-39.4</v>
+        <v>0.7753304904524825</v>
       </c>
       <c r="E44" t="n">
-        <v>1552.36</v>
+        <v>0.6011373694252871</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>39.9</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>40.55671522623627</v>
       </c>
       <c r="D45" t="n">
-        <v>-39.9</v>
+        <v>0.6567152262362725</v>
       </c>
       <c r="E45" t="n">
-        <v>1592.01</v>
+        <v>0.4312748883705586</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.1</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>39.82127980303167</v>
       </c>
       <c r="D46" t="n">
-        <v>-40.1</v>
+        <v>-0.2787201969683295</v>
       </c>
       <c r="E46" t="n">
-        <v>1608.01</v>
+        <v>0.07768494819806439</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.6</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>41.07048346559269</v>
       </c>
       <c r="D47" t="n">
-        <v>-40.6</v>
+        <v>0.4704834655926859</v>
       </c>
       <c r="E47" t="n">
-        <v>1648.36</v>
+        <v>0.2213546913961041</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.9</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>41.20638962912913</v>
       </c>
       <c r="D48" t="n">
-        <v>-40.9</v>
+        <v>0.3063896291291286</v>
       </c>
       <c r="E48" t="n">
-        <v>1672.81</v>
+        <v>0.09387460483788497</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.2</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>40.99995527419783</v>
       </c>
       <c r="D49" t="n">
-        <v>-41.2</v>
+        <v>-0.2000447258021723</v>
       </c>
       <c r="E49" t="n">
-        <v>1697.44</v>
+        <v>0.04001789232126628</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.5</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>40.57784530211027</v>
       </c>
       <c r="D50" t="n">
-        <v>-41.5</v>
+        <v>-0.9221546978897308</v>
       </c>
       <c r="E50" t="n">
-        <v>1722.25</v>
+        <v>0.8503692868401007</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.8</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>40.81076977103093</v>
       </c>
       <c r="D51" t="n">
-        <v>-41.8</v>
+        <v>-0.9892302289690704</v>
       </c>
       <c r="E51" t="n">
-        <v>1747.24</v>
+        <v>0.9785764459061995</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1689.58</v>
+        <v>-1.467507383607021</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>57846.3466</v>
+        <v>7.944572788846846</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1156.926932</v>
+        <v>0.1588914557769369</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_5.xlsx
+++ b/full/sliding_window_results_window_5.xlsx
@@ -463,13 +463,13 @@
         <v>29.54</v>
       </c>
       <c r="C2" t="n">
-        <v>29.49466895192899</v>
+        <v>29.31511894663704</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04533104807100585</v>
+        <v>-0.2248810533629637</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002054903919215843</v>
+        <v>0.05057148816163613</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.55</v>
       </c>
       <c r="C3" t="n">
-        <v>30.36079783735651</v>
+        <v>29.52533689793849</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8107978373565139</v>
+        <v>-0.02466310206150624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.657393133062</v>
+        <v>0.0006082686032962732</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.75</v>
       </c>
       <c r="C4" t="n">
-        <v>30.1949703584952</v>
+        <v>29.66880681310219</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4449703584951976</v>
+        <v>-0.08119318689781352</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1979986199393447</v>
+        <v>0.006592333598623277</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.84</v>
       </c>
       <c r="C5" t="n">
-        <v>29.99044595807602</v>
+        <v>29.79644993317601</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1504459580760162</v>
+        <v>-0.0435500668239861</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02263398630141044</v>
+        <v>0.001896608320373655</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.81</v>
       </c>
       <c r="C6" t="n">
-        <v>29.95599739102165</v>
+        <v>29.85472671013694</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1459973910216554</v>
+        <v>0.04472671013693841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02131523818513015</v>
+        <v>0.002000478599673709</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>29.86940292917211</v>
+        <v>29.73133899177474</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05059707082789089</v>
+        <v>-0.1886610082252602</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002560063576362607</v>
+        <v>0.0355929760245717</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.98</v>
       </c>
       <c r="C8" t="n">
-        <v>30.08088788470883</v>
+        <v>29.98231703795048</v>
       </c>
       <c r="D8" t="n">
-        <v>0.100887884708829</v>
+        <v>0.002317037950479772</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01017836528102198</v>
+        <v>5.368664863963503e-06</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.04</v>
       </c>
       <c r="C9" t="n">
-        <v>30.14308335558982</v>
+        <v>30.01447526087732</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1030833555898241</v>
+        <v>-0.02552473912268027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01062617819965811</v>
+        <v>0.0006515123072808849</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.21</v>
       </c>
       <c r="C10" t="n">
-        <v>30.15444665640283</v>
+        <v>29.90371187460341</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.05555334359717534</v>
+        <v>-0.3062881253965912</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003086173984825823</v>
+        <v>0.09381241575895799</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.22</v>
       </c>
       <c r="C11" t="n">
-        <v>30.41531845668382</v>
+        <v>29.95349427703949</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1953184566838218</v>
+        <v>-0.2665057229605097</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03814929952134995</v>
+        <v>0.07102530037070393</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.38</v>
       </c>
       <c r="C12" t="n">
-        <v>30.1655915532424</v>
+        <v>30.01981252053401</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2144084467575986</v>
+        <v>-0.3601874794659885</v>
       </c>
       <c r="E12" t="n">
-        <v>0.045970982041006</v>
+        <v>0.1297350203640619</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.44</v>
       </c>
       <c r="C13" t="n">
-        <v>30.31270043564337</v>
+        <v>30.10483735025484</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1272995643566297</v>
+        <v>-0.3351626497451647</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01620517908538771</v>
+        <v>0.1123340017842</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.48</v>
       </c>
       <c r="C14" t="n">
-        <v>30.46299789611383</v>
+        <v>30.35668863104404</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.01700210388616696</v>
+        <v>-0.1233113689559637</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0002890715365560138</v>
+        <v>0.01520569371379382</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.69</v>
       </c>
       <c r="C15" t="n">
-        <v>30.37324704666575</v>
+        <v>30.60752237815311</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3167529533342552</v>
+        <v>-0.08247762184689478</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1003324334459729</v>
+        <v>0.006802558105519375</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.75</v>
       </c>
       <c r="C16" t="n">
-        <v>30.12706205312848</v>
+        <v>30.27638651884344</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6229379468715237</v>
+        <v>-0.4736134811565584</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3880516856525093</v>
+        <v>0.2243097295332337</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.94</v>
       </c>
       <c r="C17" t="n">
-        <v>30.34781970634466</v>
+        <v>30.65434961214413</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5921802936553426</v>
+        <v>-0.2856503878558705</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3506775001937278</v>
+        <v>0.08159614408220925</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.95</v>
       </c>
       <c r="C18" t="n">
-        <v>30.50366043477329</v>
+        <v>30.76585366014345</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4463395652267117</v>
+        <v>-0.1841463398565502</v>
       </c>
       <c r="E18" t="n">
-        <v>0.19921900748677</v>
+        <v>0.03390987448256407</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.02</v>
       </c>
       <c r="C19" t="n">
-        <v>30.65607259769465</v>
+        <v>31.00352944902225</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3639274023053538</v>
+        <v>-0.01647055097775407</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1324431541487228</v>
+        <v>0.0002712790495107956</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.12</v>
       </c>
       <c r="C20" t="n">
-        <v>30.81190346429251</v>
+        <v>31.18213043861589</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3080965357074881</v>
+        <v>0.06213043861589185</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09492347531495547</v>
+        <v>0.003860191402603105</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.28</v>
       </c>
       <c r="C21" t="n">
-        <v>31.18871156966965</v>
+        <v>31.36224718816543</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09128843033035139</v>
+        <v>0.0822471881654252</v>
       </c>
       <c r="E21" t="n">
-        <v>0.008333577512179419</v>
+        <v>0.006764599961118859</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.38</v>
       </c>
       <c r="C22" t="n">
-        <v>31.34030125405312</v>
+        <v>31.4958110784373</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.03969874594687539</v>
+        <v>0.1158110784373036</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001575990429754555</v>
+        <v>0.0134122058888113</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.58</v>
       </c>
       <c r="C23" t="n">
-        <v>31.54362987658435</v>
+        <v>31.69217185910122</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.03637012341564372</v>
+        <v>0.112171859101224</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001322785877269155</v>
+        <v>0.01258252597422484</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.65</v>
       </c>
       <c r="C24" t="n">
-        <v>31.55541674467346</v>
+        <v>31.51188778025044</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09458325532654044</v>
+        <v>-0.1381122197495586</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00894599218816554</v>
+        <v>0.01907498524415036</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.88</v>
       </c>
       <c r="C25" t="n">
-        <v>31.83179620430884</v>
+        <v>31.72290423296682</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04820379569115474</v>
+        <v>-0.1570957670331836</v>
       </c>
       <c r="E25" t="n">
-        <v>0.002323605919034588</v>
+        <v>0.0246790800197443</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.28</v>
       </c>
       <c r="C26" t="n">
-        <v>32.25044675589361</v>
+        <v>32.03241417204158</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.02955324410639548</v>
+        <v>-0.2475858279584244</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0008733942372121993</v>
+        <v>0.06129874220585854</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.45</v>
       </c>
       <c r="C27" t="n">
-        <v>32.25729989508818</v>
+        <v>31.9887255618906</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1927001049118218</v>
+        <v>-0.4612744381094025</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03713333043302711</v>
+        <v>0.212774107253145</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.85</v>
       </c>
       <c r="C28" t="n">
-        <v>33.36429149320447</v>
+        <v>33.13550686717512</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5142914932044675</v>
+        <v>0.2855068671751226</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2644957399824809</v>
+        <v>0.08151417120415312</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.9</v>
       </c>
       <c r="C29" t="n">
-        <v>33.14803942832026</v>
+        <v>32.67128514950758</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2480394283202614</v>
+        <v>-0.2287148504924232</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06152355800144208</v>
+        <v>0.05231048283577151</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.1</v>
       </c>
       <c r="C30" t="n">
-        <v>33.38757620345185</v>
+        <v>33.11217762940498</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2875762034518488</v>
+        <v>0.0121776294049738</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08270007279177911</v>
+        <v>0.0001482946579248825</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.4</v>
       </c>
       <c r="C31" t="n">
-        <v>33.28909050317021</v>
+        <v>33.20897878926308</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.110909496829791</v>
+        <v>-0.1910212107369205</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01230091648703742</v>
+        <v>0.03648910295139898</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.7</v>
       </c>
       <c r="C32" t="n">
-        <v>33.92475531782942</v>
+        <v>33.6470833372106</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2247553178294197</v>
+        <v>-0.0529166627894071</v>
       </c>
       <c r="E32" t="n">
-        <v>0.05051495289260347</v>
+        <v>0.002800173200767822</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.1</v>
       </c>
       <c r="C33" t="n">
-        <v>34.66902840265841</v>
+        <v>34.23243248585688</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5690284026584038</v>
+        <v>0.1324324858568815</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3237933230319746</v>
+        <v>0.01753836331023312</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.4</v>
       </c>
       <c r="C34" t="n">
-        <v>34.63718235691104</v>
+        <v>34.27142069441706</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2371823569110418</v>
+        <v>-0.1285793055829387</v>
       </c>
       <c r="E34" t="n">
-        <v>0.05625547042987684</v>
+        <v>0.01653263782419074</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.9</v>
       </c>
       <c r="C35" t="n">
-        <v>35.05672620621896</v>
+        <v>35.05731837910608</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1567262062189627</v>
+        <v>0.1573183791060799</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02456310371578883</v>
+        <v>0.02474907240456429</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>35.3</v>
       </c>
       <c r="C36" t="n">
-        <v>34.87466341241493</v>
+        <v>34.78061190415429</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4253365875850719</v>
+        <v>-0.5193880958457058</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1809112127385135</v>
+        <v>0.269763994106228</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>35.7</v>
       </c>
       <c r="C37" t="n">
-        <v>35.17604680191488</v>
+        <v>35.25630578183572</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.523953198085124</v>
+        <v>-0.443694218164282</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2745269537836292</v>
+        <v>0.1968645592324135</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>36.3</v>
       </c>
       <c r="C38" t="n">
-        <v>35.79052169454162</v>
+        <v>36.1639103465651</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.50947830545838</v>
+        <v>-0.1360896534348939</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2595681437327424</v>
+        <v>0.01852039377202952</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>36.8</v>
       </c>
       <c r="C39" t="n">
-        <v>36.17600804826044</v>
+        <v>36.53305326735197</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.623991951739562</v>
+        <v>-0.2669467326480301</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3893659558357479</v>
+        <v>0.07126055807145888</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>37.3</v>
       </c>
       <c r="C40" t="n">
-        <v>37.20473327999652</v>
+        <v>37.24528631886898</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.09526672000347958</v>
+        <v>-0.0547136811310196</v>
       </c>
       <c r="E40" t="n">
-        <v>0.009075747940221375</v>
+        <v>0.00299358690290689</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>37.9</v>
       </c>
       <c r="C41" t="n">
-        <v>37.80274794948554</v>
+        <v>37.81848028722173</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.09725205051446295</v>
+        <v>-0.08151971277826675</v>
       </c>
       <c r="E41" t="n">
-        <v>0.009457961329267654</v>
+        <v>0.006645463571451108</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>38.5</v>
       </c>
       <c r="C42" t="n">
-        <v>38.56262667401201</v>
+        <v>38.21203912419593</v>
       </c>
       <c r="D42" t="n">
-        <v>0.06262667401200872</v>
+        <v>-0.2879608758040675</v>
       </c>
       <c r="E42" t="n">
-        <v>0.003922100297806408</v>
+        <v>0.08292146599384558</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>38.9</v>
       </c>
       <c r="C43" t="n">
-        <v>39.44100861461524</v>
+        <v>38.7411190974552</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5410086146152366</v>
+        <v>-0.1588809025447944</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2926903210878977</v>
+        <v>0.02524314119344844</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>39.4</v>
       </c>
       <c r="C44" t="n">
-        <v>40.17533049045248</v>
+        <v>39.24940906054054</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7753304904524825</v>
+        <v>-0.1505909394594624</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6011373694252871</v>
+        <v>0.02267763104728348</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>39.9</v>
       </c>
       <c r="C45" t="n">
-        <v>40.55671522623627</v>
+        <v>39.63572927498696</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6567152262362725</v>
+        <v>-0.2642707250130414</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4312748883705586</v>
+        <v>0.06983901609891854</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.1</v>
       </c>
       <c r="C46" t="n">
-        <v>39.82127980303167</v>
+        <v>40.28024491551957</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2787201969683295</v>
+        <v>0.180244915519566</v>
       </c>
       <c r="E46" t="n">
-        <v>0.07768494819806439</v>
+        <v>0.03248822957065549</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.6</v>
       </c>
       <c r="C47" t="n">
-        <v>41.07048346559269</v>
+        <v>40.41132527535378</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4704834655926859</v>
+        <v>-0.1886747246462264</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2213546913961041</v>
+        <v>0.03559815172032934</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.9</v>
       </c>
       <c r="C48" t="n">
-        <v>41.20638962912913</v>
+        <v>41.05647139128535</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3063896291291286</v>
+        <v>0.1564713912853506</v>
       </c>
       <c r="E48" t="n">
-        <v>0.09387460483788497</v>
+        <v>0.02448329629077329</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.2</v>
       </c>
       <c r="C49" t="n">
-        <v>40.99995527419783</v>
+        <v>41.32974621400539</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2000447258021723</v>
+        <v>0.1297462140053867</v>
       </c>
       <c r="E49" t="n">
-        <v>0.04001789232126628</v>
+        <v>0.01683408004873159</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.5</v>
       </c>
       <c r="C50" t="n">
-        <v>40.57784530211027</v>
+        <v>40.99679168892736</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.9221546978897308</v>
+        <v>-0.5032083110726404</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8503692868401007</v>
+        <v>0.2532186043325793</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.8</v>
       </c>
       <c r="C51" t="n">
-        <v>40.81076977103093</v>
+        <v>41.25082734706558</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.9892302289690704</v>
+        <v>-0.5491726529344163</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9785764459061995</v>
+        <v>0.3015906027310249</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1.467507383607021</v>
+        <v>-6.759396197880537</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>7.944572788846846</v>
+        <v>2.884392562547813</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1588914557769369</v>
+        <v>0.05768785125095625</v>
       </c>
     </row>
   </sheetData>
